--- a/eval/visualization/outputs/data/model_skills_report.xlsx
+++ b/eval/visualization/outputs/data/model_skills_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="93">
   <si>
     <t>Domain</t>
   </si>
@@ -134,6 +134,69 @@
     <t>PowerPoint: Add Agenda Slide After Title Slide</t>
   </si>
   <si>
+    <t>google-workspace-gws-cli</t>
+  </si>
+  <si>
+    <t>EVAL_GWS_001</t>
+  </si>
+  <si>
+    <t>Gmail: Unread Inbox Triage &amp; Sender Domain Breakdown</t>
+  </si>
+  <si>
+    <t>gws-gmail-triage</t>
+  </si>
+  <si>
+    <t>EVAL_GWS_002</t>
+  </si>
+  <si>
+    <t>Gmail: Smart Draft Replies for a Project Thread</t>
+  </si>
+  <si>
+    <t>gws-gmail</t>
+  </si>
+  <si>
+    <t>EVAL_GWS_003</t>
+  </si>
+  <si>
+    <t>Google Calendar: Full Week Audit — Conflicts &amp; Free Time</t>
+  </si>
+  <si>
+    <t>EVAL_GWS_004</t>
+  </si>
+  <si>
+    <t>Gmail: Thread Summarization &amp; Action Item Extraction</t>
+  </si>
+  <si>
+    <t>EVAL_GWS_005</t>
+  </si>
+  <si>
+    <t>Google Drive: File Hygiene Audit — Stale, Oversized &amp; Public Files</t>
+  </si>
+  <si>
+    <t>gws-drive</t>
+  </si>
+  <si>
+    <t>EVAL_GWS_006</t>
+  </si>
+  <si>
+    <t>Google Drive: Folder Summary Report Written to a New Google Doc</t>
+  </si>
+  <si>
+    <t>EVAL_GWS_007</t>
+  </si>
+  <si>
+    <t>Google Calendar: Next 14 Days — Recurring Event Audit</t>
+  </si>
+  <si>
+    <t>gws-calendar-agenda</t>
+  </si>
+  <si>
+    <t>EVAL_GWS_008</t>
+  </si>
+  <si>
+    <t>Gmail: Sent Mail Analysis — Response Rate &amp; Top Contacts</t>
+  </si>
+  <si>
     <t>web-browsing-hard-agent-browser</t>
   </si>
   <si>
@@ -213,6 +276,21 @@
   </si>
   <si>
     <t>docx, pdf, xlsx</t>
+  </si>
+  <si>
+    <t>gws-gmail, gws-gmail-triage</t>
+  </si>
+  <si>
+    <t>gws-drive, gws-shared</t>
+  </si>
+  <si>
+    <t>gws-calendar, gws-calendar-agenda</t>
+  </si>
+  <si>
+    <t>gws-gmail, gws-gmail-send</t>
+  </si>
+  <si>
+    <t>gws-calendar</t>
   </si>
   <si>
     <t>agent-browser, pinchtab</t>
@@ -596,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -812,7 +890,7 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -966,7 +1044,7 @@
         <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -974,13 +1052,13 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -988,13 +1066,13 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1002,13 +1080,13 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1016,13 +1094,13 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1030,13 +1108,13 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1044,192 +1122,192 @@
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>60</v>
       </c>
-      <c r="D38" t="s">
-        <v>42</v>
+      <c r="B39" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C43" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D43" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D45" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" t="s">
         <v>61</v>
       </c>
-      <c r="B48" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="C51" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" t="s">
-        <v>58</v>
-      </c>
-      <c r="D49" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>61</v>
-      </c>
-      <c r="B50" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" t="s">
-        <v>60</v>
-      </c>
-      <c r="D50" t="s">
-        <v>62</v>
+      <c r="D51" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -1237,127 +1315,239 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C55" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B57" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B58" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C58" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B60" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C60" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>63</v>
-      </c>
-      <c r="B61" t="s">
-        <v>57</v>
-      </c>
-      <c r="C61" t="s">
-        <v>58</v>
-      </c>
-      <c r="D61" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>63</v>
-      </c>
-      <c r="B62" t="s">
-        <v>59</v>
-      </c>
-      <c r="C62" t="s">
-        <v>60</v>
-      </c>
-      <c r="D62" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" t="s">
+        <v>61</v>
+      </c>
+      <c r="C63" t="s">
+        <v>62</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" t="s">
+        <v>64</v>
+      </c>
+      <c r="C64" t="s">
+        <v>65</v>
+      </c>
+      <c r="D64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" t="s">
+        <v>66</v>
+      </c>
+      <c r="C65" t="s">
+        <v>67</v>
+      </c>
+      <c r="D65" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>84</v>
+      </c>
+      <c r="B66" t="s">
+        <v>68</v>
+      </c>
+      <c r="C66" t="s">
+        <v>69</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" t="s">
+        <v>70</v>
+      </c>
+      <c r="C67" t="s">
+        <v>71</v>
+      </c>
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" t="s">
+        <v>73</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" t="s">
+        <v>75</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" t="s">
+        <v>76</v>
+      </c>
+      <c r="C70" t="s">
+        <v>77</v>
+      </c>
+      <c r="D70" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" t="s">
+        <v>78</v>
+      </c>
+      <c r="C71" t="s">
+        <v>79</v>
+      </c>
+      <c r="D71" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>84</v>
+      </c>
+      <c r="B72" t="s">
+        <v>80</v>
+      </c>
+      <c r="C72" t="s">
+        <v>81</v>
+      </c>
+      <c r="D72" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1369,7 +1559,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1431,7 +1621,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1543,7 +1733,7 @@
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1641,7 +1831,7 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1725,7 +1915,7 @@
         <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1733,13 +1923,13 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1747,13 +1937,13 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1761,13 +1951,13 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1775,13 +1965,13 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1789,13 +1979,13 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1803,262 +1993,262 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>60</v>
       </c>
-      <c r="D37" t="s">
-        <v>42</v>
+      <c r="B38" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" t="s">
         <v>61</v>
       </c>
-      <c r="B47" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>61</v>
-      </c>
-      <c r="B48" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" t="s">
-        <v>58</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="C50" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" t="s">
-        <v>60</v>
-      </c>
-      <c r="D49" t="s">
-        <v>62</v>
+      <c r="D50" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" t="s">
+        <v>65</v>
+      </c>
+      <c r="D51" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C54" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B57" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -2066,57 +2256,169 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C59" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" t="s">
-        <v>57</v>
-      </c>
-      <c r="C60" t="s">
-        <v>58</v>
-      </c>
-      <c r="D60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>63</v>
-      </c>
-      <c r="B61" t="s">
-        <v>59</v>
-      </c>
-      <c r="C61" t="s">
-        <v>60</v>
-      </c>
-      <c r="D61" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>84</v>
+      </c>
+      <c r="B62" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" t="s">
+        <v>62</v>
+      </c>
+      <c r="D62" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" t="s">
+        <v>65</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>84</v>
+      </c>
+      <c r="B66" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" t="s">
+        <v>73</v>
+      </c>
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" t="s">
+        <v>77</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" t="s">
+        <v>81</v>
+      </c>
+      <c r="D71" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2128,7 +2430,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -2400,7 +2702,7 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2470,7 +2772,7 @@
         <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2484,7 +2786,7 @@
         <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2492,13 +2794,13 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2506,13 +2808,13 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2520,13 +2822,13 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2534,13 +2836,13 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2548,13 +2850,13 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2562,320 +2864,432 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>60</v>
       </c>
-      <c r="D37" t="s">
-        <v>42</v>
+      <c r="B38" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" t="s">
         <v>61</v>
       </c>
-      <c r="B47" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C50" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>61</v>
-      </c>
-      <c r="B48" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" t="s">
-        <v>58</v>
-      </c>
-      <c r="D48" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" t="s">
-        <v>60</v>
-      </c>
-      <c r="D49" t="s">
-        <v>62</v>
+      <c r="D50" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" t="s">
+        <v>65</v>
+      </c>
+      <c r="D51" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C54" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B57" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C59" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" t="s">
-        <v>57</v>
-      </c>
-      <c r="C60" t="s">
-        <v>58</v>
-      </c>
-      <c r="D60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>63</v>
-      </c>
-      <c r="B61" t="s">
-        <v>59</v>
-      </c>
-      <c r="C61" t="s">
-        <v>60</v>
-      </c>
-      <c r="D61" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>84</v>
+      </c>
+      <c r="B62" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" t="s">
+        <v>62</v>
+      </c>
+      <c r="D62" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" t="s">
+        <v>65</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>84</v>
+      </c>
+      <c r="B66" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" t="s">
+        <v>73</v>
+      </c>
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" t="s">
+        <v>77</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" t="s">
+        <v>81</v>
+      </c>
+      <c r="D71" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2887,7 +3301,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -3159,7 +3573,7 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3229,7 +3643,7 @@
         <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3243,7 +3657,7 @@
         <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -3251,13 +3665,13 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3265,13 +3679,13 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3279,13 +3693,13 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3293,13 +3707,13 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3307,13 +3721,13 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3321,320 +3735,432 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>60</v>
       </c>
-      <c r="D37" t="s">
-        <v>42</v>
+      <c r="B38" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" t="s">
         <v>61</v>
       </c>
-      <c r="B47" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C50" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>61</v>
-      </c>
-      <c r="B48" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" t="s">
-        <v>58</v>
-      </c>
-      <c r="D48" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" t="s">
-        <v>60</v>
-      </c>
-      <c r="D49" t="s">
-        <v>62</v>
+      <c r="D50" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" t="s">
+        <v>65</v>
+      </c>
+      <c r="D51" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C54" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B57" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C59" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" t="s">
-        <v>57</v>
-      </c>
-      <c r="C60" t="s">
-        <v>58</v>
-      </c>
-      <c r="D60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>63</v>
-      </c>
-      <c r="B61" t="s">
-        <v>59</v>
-      </c>
-      <c r="C61" t="s">
-        <v>60</v>
-      </c>
-      <c r="D61" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>84</v>
+      </c>
+      <c r="B62" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" t="s">
+        <v>62</v>
+      </c>
+      <c r="D62" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" t="s">
+        <v>65</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>84</v>
+      </c>
+      <c r="B66" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" t="s">
+        <v>73</v>
+      </c>
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" t="s">
+        <v>77</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" t="s">
+        <v>81</v>
+      </c>
+      <c r="D71" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3646,7 +4172,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -3918,7 +4444,7 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3988,7 +4514,7 @@
         <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -4002,7 +4528,7 @@
         <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -4010,13 +4536,13 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -4024,13 +4550,13 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -4038,13 +4564,13 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -4052,13 +4578,13 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -4066,13 +4592,13 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -4080,320 +4606,432 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>60</v>
       </c>
-      <c r="D37" t="s">
-        <v>42</v>
+      <c r="B38" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" t="s">
         <v>61</v>
       </c>
-      <c r="B47" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>61</v>
-      </c>
-      <c r="B48" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" t="s">
-        <v>58</v>
-      </c>
-      <c r="D48" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" t="s">
-        <v>60</v>
-      </c>
-      <c r="D49" t="s">
-        <v>42</v>
+      <c r="C50" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" t="s">
+        <v>65</v>
+      </c>
+      <c r="D51" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C54" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B57" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C59" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" t="s">
-        <v>57</v>
-      </c>
-      <c r="C60" t="s">
-        <v>58</v>
-      </c>
-      <c r="D60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>63</v>
-      </c>
-      <c r="B61" t="s">
-        <v>59</v>
-      </c>
-      <c r="C61" t="s">
-        <v>60</v>
-      </c>
-      <c r="D61" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>84</v>
+      </c>
+      <c r="B62" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" t="s">
+        <v>62</v>
+      </c>
+      <c r="D62" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" t="s">
+        <v>65</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>84</v>
+      </c>
+      <c r="B66" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" t="s">
+        <v>73</v>
+      </c>
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" t="s">
+        <v>77</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" t="s">
+        <v>81</v>
+      </c>
+      <c r="D71" t="s">
         <v>7</v>
       </c>
     </row>

--- a/eval/visualization/outputs/data/model_skills_report.xlsx
+++ b/eval/visualization/outputs/data/model_skills_report.xlsx
@@ -9,13 +9,14 @@
     <sheet sheetId="3" name="gpt-5.3-codex" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="grok-code-fast-1" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="minimax-m2.5-free" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="fm_skill_trigger_rate" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="103">
   <si>
     <t>Domain</t>
   </si>
@@ -294,6 +295,36 @@
   </si>
   <si>
     <t>agent-browser, pinchtab</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Checked Tasks</t>
+  </si>
+  <si>
+    <t>Triggered Tasks</t>
+  </si>
+  <si>
+    <t>Trigger Rate (%)</t>
+  </si>
+  <si>
+    <t>github-copilot_claude-sonnet-4.6</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>github-copilot_gemini-3-flash-preview</t>
+  </si>
+  <si>
+    <t>github-copilot_gpt-5.3-codex</t>
+  </si>
+  <si>
+    <t>github-copilot_grok-code-fast-1</t>
+  </si>
+  <si>
+    <t>opencode_minimax-m2.5-free</t>
   </si>
 </sst>
 </file>
@@ -332,9 +363,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5039,4 +5072,342 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16" style="2" customWidth="1"/>
+    <col min="6" max="9" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>75</v>
+      </c>
+      <c r="F2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2">
+        <v>100</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>50</v>
+      </c>
+      <c r="F4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>100</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>100</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2">
+        <v>50</v>
+      </c>
+      <c r="F10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>75</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/eval/visualization/outputs/data/model_skills_report.xlsx
+++ b/eval/visualization/outputs/data/model_skills_report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="102">
   <si>
     <t>Domain</t>
   </si>
@@ -292,9 +292,6 @@
   </si>
   <si>
     <t>gws-calendar</t>
-  </si>
-  <si>
-    <t>agent-browser, pinchtab</t>
   </si>
   <si>
     <t>Model</t>
@@ -1343,7 +1340,7 @@
         <v>67</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1371,7 +1368,7 @@
         <v>71</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2278,13 +2275,13 @@
         <v>82</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2292,10 +2289,10 @@
         <v>82</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D58" t="s">
         <v>83</v>
@@ -2306,10 +2303,10 @@
         <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C59" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D59" t="s">
         <v>83</v>
@@ -4793,13 +4790,13 @@
         <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -4807,13 +4804,13 @@
         <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -4821,10 +4818,10 @@
         <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D52" t="s">
         <v>83</v>
@@ -4835,10 +4832,10 @@
         <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
         <v>83</v>
@@ -4849,13 +4846,13 @@
         <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C54" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D54" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -4863,10 +4860,10 @@
         <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C55" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D55" t="s">
         <v>83</v>
@@ -4883,7 +4880,7 @@
         <v>75</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -4897,7 +4894,7 @@
         <v>77</v>
       </c>
       <c r="D57" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -4911,7 +4908,7 @@
         <v>79</v>
       </c>
       <c r="D58" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -4925,7 +4922,7 @@
         <v>81</v>
       </c>
       <c r="D59" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -5089,19 +5086,19 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -5118,7 +5115,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -5133,7 +5130,7 @@
         <v>75</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
@@ -5147,7 +5144,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
         <v>28</v>
@@ -5176,7 +5173,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -5191,7 +5188,7 @@
         <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
@@ -5200,12 +5197,12 @@
         <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
@@ -5234,7 +5231,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -5249,7 +5246,7 @@
         <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
@@ -5258,12 +5255,12 @@
         <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
@@ -5292,7 +5289,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -5307,7 +5304,7 @@
         <v>50</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
@@ -5316,12 +5313,12 @@
         <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
@@ -5350,7 +5347,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -5365,7 +5362,7 @@
         <v>50</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
@@ -5374,12 +5371,12 @@
         <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
@@ -5400,7 +5397,7 @@
         <v>10</v>
       </c>
       <c r="H11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I11" t="s">
         <v>27</v>

--- a/eval/visualization/outputs/data/model_skills_report.xlsx
+++ b/eval/visualization/outputs/data/model_skills_report.xlsx
@@ -10,13 +10,14 @@
     <sheet sheetId="4" name="grok-code-fast-1" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="minimax-m2.5-free" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="fm_skill_trigger_rate" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="pinchtab_cli_usage" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="105">
   <si>
     <t>Domain</t>
   </si>
@@ -322,6 +323,15 @@
   </si>
   <si>
     <t>opencode_minimax-m2.5-free</t>
+  </si>
+  <si>
+    <t>Pinchtab Tests</t>
+  </si>
+  <si>
+    <t>CLI Usage Tool Calls</t>
+  </si>
+  <si>
+    <t>curl.exe Usage Tool Calls</t>
   </si>
 </sst>
 </file>
@@ -5407,4 +5417,105 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>115</v>
+      </c>
+      <c r="D2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>180</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>76</v>
+      </c>
+      <c r="D4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>75</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>130</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>